--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_340_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_340_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M2" t="n">
         <v>12</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M3" t="n">
         <v>20</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,16 +1335,16 @@
         <v>29</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
         <v>12</v>
@@ -1733,10 +1733,10 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X19" t="n">
         <v>5</v>
@@ -2119,7 +2119,7 @@
         <v>7</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2315,16 +2315,16 @@
         <v>34</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X22" t="n">
         <v>11</v>
@@ -2707,16 +2707,16 @@
         <v>16</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X24" t="n">
         <v>3</v>
@@ -2909,10 +2909,10 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -3301,10 +3301,10 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X27" t="n">
         <v>4</v>
@@ -3631,16 +3631,16 @@
         <v>131</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X29" t="n">
         <v>39</v>
@@ -4102,10 +4102,10 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X34" t="n">
         <v>8</v>
@@ -4292,10 +4292,10 @@
         <v>25</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -4687,13 +4687,13 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X37" t="n">
         <v>9</v>
@@ -5082,10 +5082,10 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" t="n">
         <v>2</v>
@@ -5278,10 +5278,10 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X40" t="n">
         <v>3</v>
@@ -5468,10 +5468,10 @@
         <v>9</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -5664,16 +5664,16 @@
         <v>6</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X42" t="n">
         <v>5</v>
@@ -5860,10 +5860,10 @@
         <v>22</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6059,7 +6059,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -6588,16 +6588,16 @@
         <v>129</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X47" t="n">
         <v>46</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_340_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_340_EL.xlsx
@@ -674,10 +674,10 @@
         <v>12</v>
       </c>
       <c r="N2" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="O2" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="P2" t="n">
         <v>7</v>
@@ -692,20 +692,20 @@
         <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="W2" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>81.25</t>
+          <t>64.00</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>34.78</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>20</v>
       </c>
       <c r="N3" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="O3" t="n">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
@@ -854,17 +854,17 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V3" t="n">
         <v>9</v>
       </c>
       <c r="W3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>90.20</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>36.00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,14 +1347,14 @@
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Y17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -1739,14 +1739,14 @@
         <v>3</v>
       </c>
       <c r="X19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y19" t="n">
         <v>5</v>
       </c>
-      <c r="Y19" t="n">
-        <v>7</v>
-      </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -1772,25 +1772,25 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -2327,14 +2327,14 @@
         <v>2</v>
       </c>
       <c r="X22" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA22" t="n">
@@ -2360,25 +2360,25 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -2719,58 +2719,58 @@
         <v>1</v>
       </c>
       <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK24" t="n">
         <v>3</v>
       </c>
-      <c r="Y24" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AA24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AJ24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>4</v>
-      </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -3111,14 +3111,14 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -3307,10 +3307,10 @@
         <v>1</v>
       </c>
       <c r="X27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
@@ -3340,25 +3340,25 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -3643,14 +3643,14 @@
         <v>9</v>
       </c>
       <c r="X29" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="Y29" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="AA29" t="n">
@@ -3676,25 +3676,25 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AH29" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AK29" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -4108,10 +4108,10 @@
         <v>2</v>
       </c>
       <c r="X34" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y34" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
@@ -4304,10 +4304,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y35" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
@@ -4696,10 +4696,10 @@
         <v>2</v>
       </c>
       <c r="X37" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Y37" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -5284,14 +5284,14 @@
         <v>2</v>
       </c>
       <c r="X40" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y40" t="n">
         <v>3</v>
       </c>
-      <c r="Y40" t="n">
-        <v>4</v>
-      </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5320,18 +5320,18 @@
         <v>1</v>
       </c>
       <c r="AH40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AJ40" t="n">
         <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
@@ -5527,11 +5527,11 @@
         <v>2</v>
       </c>
       <c r="AK41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
@@ -5676,10 +5676,10 @@
         <v>1</v>
       </c>
       <c r="X42" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y42" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
@@ -5872,10 +5872,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y43" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
@@ -6600,14 +6600,14 @@
         <v>8</v>
       </c>
       <c r="X47" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="Y47" t="n">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="AA47" t="n">
@@ -6636,22 +6636,22 @@
         <v>1</v>
       </c>
       <c r="AH47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AJ47" t="n">
         <v>9</v>
       </c>
       <c r="AK47" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
